--- a/Result/profitability/3701.xlsx
+++ b/Result/profitability/3701.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM84"/>
+  <dimension ref="A1:AM85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,10 +667,10 @@
         <v>-1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.315</v>
+        <v>-0.39</v>
       </c>
       <c r="N2" t="n">
-        <v>14.625</v>
+        <v>14.2375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -776,10 +776,10 @@
         <v>-1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5</v>
+        <v>-0.57625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.6375</v>
+        <v>12.9725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -893,10 +893,10 @@
         <v>-1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.65125</v>
+        <v>-0.8225</v>
       </c>
       <c r="N4" t="n">
-        <v>12.53625</v>
+        <v>11.74625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1010,10 +1010,10 @@
         <v>-1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-1.0575</v>
       </c>
       <c r="N5" t="n">
-        <v>11.42</v>
+        <v>10.10625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1127,10 +1127,10 @@
         <v>-1.18</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1175</v>
+        <v>-1.225</v>
       </c>
       <c r="N6" t="n">
-        <v>9.807499999999999</v>
+        <v>8.782500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1252,10 +1252,10 @@
         <v>-1.29</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.29875</v>
+        <v>-1.20125</v>
       </c>
       <c r="N7" t="n">
-        <v>8.5425</v>
+        <v>7.89375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>-1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.26875</v>
+        <v>-1.2825</v>
       </c>
       <c r="N8" t="n">
-        <v>7.404999999999999</v>
+        <v>6.850000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1630,7 +1630,7 @@
         <v>-0.9037500000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>6.765</v>
+        <v>6.765000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1882,7 +1882,7 @@
         <v>-1.13375</v>
       </c>
       <c r="N12" t="n">
-        <v>7.260000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -11084,6 +11084,133 @@
       </c>
       <c r="AM84" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3701</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2096</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1890</v>
+      </c>
+      <c r="E85" t="n">
+        <v>206</v>
+      </c>
+      <c r="F85" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-246</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-11.72%</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>-38</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-284</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-165</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M85" t="n">
+        <v>-0.23125</v>
+      </c>
+      <c r="N85" t="n">
+        <v>15.225</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W85" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="X85" t="n">
+        <v>0.1864406779661016</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>-4.44</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>-0.3109243697478992</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>-0.5164619164619165</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK85" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
